--- a/GBU 2301/datasets/BankBranchMonthly.xlsx
+++ b/GBU 2301/datasets/BankBranchMonthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e744a0cafea0a387/CBU/_Teaching/AUI/Business Statistics/GBU 2301/datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_0BCED763772FEB5B256097D0F36648C402A2DE57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1095DA7E-F528-404B-B7F2-2843A2707E37}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_0BCED763772FEB5B256097D0F36648C402A2DE57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2823E150-826F-4328-8D20-5CA438DE6C99}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
